--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.044018332561897</v>
+        <v>1.144652979041308</v>
       </c>
       <c r="D2" t="n">
-        <v>5.634422253781515</v>
+        <v>0.9155936162394962</v>
       </c>
       <c r="E2" t="n">
-        <v>11.89237676330688</v>
+        <v>1.932511224037369</v>
       </c>
       <c r="F2" t="n">
-        <v>4.578027618323637</v>
+        <v>0.743929487977591</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.40802391346406</v>
+        <v>5.916303885937911</v>
       </c>
       <c r="D3" t="n">
-        <v>13.42150864987479</v>
+        <v>2.180995155604653</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89237676330688</v>
+        <v>1.932511224037369</v>
       </c>
       <c r="F3" t="n">
-        <v>4.578027618323637</v>
+        <v>0.743929487977591</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.21953612320214</v>
+        <v>3.610674620020347</v>
       </c>
       <c r="D4" t="n">
-        <v>4.462146243600259</v>
+        <v>0.7250987645850421</v>
       </c>
       <c r="E4" t="n">
-        <v>11.89237676330688</v>
+        <v>1.932511224037369</v>
       </c>
       <c r="F4" t="n">
-        <v>4.578027618323637</v>
+        <v>0.743929487977591</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.502485834626304</v>
+        <v>1.381653948126774</v>
       </c>
       <c r="D5" t="n">
-        <v>14.80648573815183</v>
+        <v>2.406053932449673</v>
       </c>
       <c r="E5" t="n">
-        <v>11.89237676330688</v>
+        <v>1.932511224037369</v>
       </c>
       <c r="F5" t="n">
-        <v>4.578027618323637</v>
+        <v>0.743929487977591</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
